--- a/tests/fixtures/bank_native/202624/2026041400/K+EUR Daily Rate PnL GVA_20260414.xlsx
+++ b/tests/fixtures/bank_native/202624/2026041400/K+EUR Daily Rate PnL GVA_20260414.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,6 +620,11 @@
       <c r="AN1" t="inlineStr">
         <is>
           <t>[Daily] PnL IAS - ORC</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Clean_Price</t>
         </is>
       </c>
     </row>
@@ -764,6 +769,7 @@
       <c r="AN2" t="n">
         <v>625</v>
       </c>
+      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -902,6 +908,7 @@
       <c r="AN3" t="n">
         <v>375</v>
       </c>
+      <c r="AO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -1044,6 +1051,7 @@
       <c r="AN4" t="n">
         <v>-333.34</v>
       </c>
+      <c r="AO4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1186,6 +1194,7 @@
       <c r="AN5" t="n">
         <v>-381.94</v>
       </c>
+      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1328,6 +1337,7 @@
       <c r="AN6" t="n">
         <v>388.89</v>
       </c>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1470,6 +1480,9 @@
       <c r="AN7" t="n">
         <v>-388.89</v>
       </c>
+      <c r="AO7" t="n">
+        <v>102.35</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1612,6 +1625,9 @@
       <c r="AN8" t="n">
         <v>-250</v>
       </c>
+      <c r="AO8" t="n">
+        <v>101.18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1754,6 +1770,9 @@
       <c r="AN9" t="n">
         <v>-291.67</v>
       </c>
+      <c r="AO9" t="n">
+        <v>102.85</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1904,6 +1923,9 @@
       <c r="AN10" t="n">
         <v>-395.83</v>
       </c>
+      <c r="AO10" t="n">
+        <v>103.52</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -2054,6 +2076,9 @@
       <c r="AN11" t="n">
         <v>-729.16</v>
       </c>
+      <c r="AO11" t="n">
+        <v>104.17</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -2200,6 +2225,7 @@
       <c r="AN12" t="n">
         <v>-1083.33</v>
       </c>
+      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -2346,6 +2372,7 @@
       <c r="AN13" t="n">
         <v>1062.5</v>
       </c>
+      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2496,6 +2523,9 @@
       <c r="AN14" t="n">
         <v>-958.33</v>
       </c>
+      <c r="AO14" t="n">
+        <v>104.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2638,6 +2668,7 @@
       <c r="AN15" t="n">
         <v>-534.73</v>
       </c>
+      <c r="AO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -2780,6 +2811,7 @@
       <c r="AN16" t="n">
         <v>-333.34</v>
       </c>
+      <c r="AO16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2922,6 +2954,7 @@
       <c r="AN17" t="n">
         <v>97.22</v>
       </c>
+      <c r="AO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -3060,6 +3093,7 @@
       <c r="AN18" t="n">
         <v>133.33</v>
       </c>
+      <c r="AO18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -3198,6 +3232,7 @@
       <c r="AN19" t="n">
         <v>-55.56</v>
       </c>
+      <c r="AO19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3210,7 +3245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL13"/>
+  <dimension ref="A1:AM13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3404,6 +3439,11 @@
           <t>[Daily] PnL MTM</t>
         </is>
       </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Clean_Price</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -3550,6 +3590,9 @@
       <c r="AL2" t="n">
         <v>-510.4</v>
       </c>
+      <c r="AM2" t="n">
+        <v>103.52</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -3696,6 +3739,9 @@
       <c r="AL3" t="n">
         <v>-972.1900000000001</v>
       </c>
+      <c r="AM3" t="n">
+        <v>104.17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -3838,6 +3884,9 @@
       <c r="AL4" t="n">
         <v>-388.88</v>
       </c>
+      <c r="AM4" t="n">
+        <v>101.94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -3976,6 +4025,7 @@
       <c r="AL5" t="n">
         <v>-3791.65</v>
       </c>
+      <c r="AM5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -4114,6 +4164,7 @@
       <c r="AL6" t="n">
         <v>3718.75</v>
       </c>
+      <c r="AM6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -4256,6 +4307,7 @@
       <c r="AL7" t="n">
         <v>2333.34</v>
       </c>
+      <c r="AM7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -4398,6 +4450,7 @@
       <c r="AL8" t="n">
         <v>-1531.25</v>
       </c>
+      <c r="AM8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -4540,6 +4593,7 @@
       <c r="AL9" t="n">
         <v>-1020.85</v>
       </c>
+      <c r="AM9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -4678,6 +4732,7 @@
       <c r="AL10" t="n">
         <v>2430.58</v>
       </c>
+      <c r="AM10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -4816,6 +4871,7 @@
       <c r="AL11" t="n">
         <v>1944.43</v>
       </c>
+      <c r="AM11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -4954,6 +5010,7 @@
       <c r="AL12" t="n">
         <v>-972.1900000000001</v>
       </c>
+      <c r="AM12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -5092,6 +5149,7 @@
       <c r="AL13" t="n">
         <v>-875</v>
       </c>
+      <c r="AM13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
